--- a/data/trans_orig/IP07A02-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP07A02-Clase-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haber podido correr bien en 2007 (tasa de respuesta: 99,4%)</t>
+          <t>Menores según la frecuencia de haber podido correr bien, percibida por el adulto en 2007 (tasa de respuesta: 99,4%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14400</t>
+          <t>14616</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25589</t>
+          <t>25402</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>53,78%</t>
+          <t>53,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19902</t>
+          <t>19400</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>29761</t>
+          <t>29717</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>48,36%</t>
+          <t>47,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>72,31%</t>
+          <t>72,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>36374</t>
+          <t>36794</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>52376</t>
+          <t>51786</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>40,99%</t>
+          <t>41,46%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>59,02%</t>
+          <t>58,36%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20034</t>
+          <t>19889</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>31403</t>
+          <t>31050</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>42,11%</t>
+          <t>41,8%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>66,0%</t>
+          <t>65,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10120</t>
+          <t>9918</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19988</t>
+          <t>20198</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>48,57%</t>
+          <t>49,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>32692</t>
+          <t>33642</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>48686</t>
+          <t>48585</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>37,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>54,87%</t>
+          <t>54,75%</t>
         </is>
       </c>
     </row>
@@ -963,7 +963,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>4774</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5673</t>
+          <t>6045</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,81%</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2686</t>
+          <t>2668</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3186</t>
+          <t>3378</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4448</t>
+          <t>4362</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,92%</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3528</t>
+          <t>3202</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3367</t>
+          <t>3637</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>4,1%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12717</t>
+          <t>12445</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21081</t>
+          <t>21132</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>42,43%</t>
+          <t>41,52%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>70,33%</t>
+          <t>70,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10433</t>
+          <t>10089</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19028</t>
+          <t>19228</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>31,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>60,06%</t>
+          <t>60,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>25183</t>
+          <t>25143</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>38541</t>
+          <t>37764</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>40,84%</t>
+          <t>40,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>62,51%</t>
+          <t>61,25%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6423</t>
+          <t>6117</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14771</t>
+          <t>14802</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>49,28%</t>
+          <t>49,38%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10727</t>
+          <t>10614</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>19640</t>
+          <t>19524</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>33,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>61,99%</t>
+          <t>61,62%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>19149</t>
+          <t>19355</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>32255</t>
+          <t>32072</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>52,31%</t>
+          <t>52,02%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>665</t>
+          <t>684</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5833</t>
+          <t>6283</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,82 +1655,82 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
+          <t>2,28%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>20,96%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>1360</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>4294</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>4,29%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>13,55%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>3992</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>1367</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>7959</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>6,47%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
           <t>2,22%</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>19,46%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>1360</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>4122</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>4,29%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>13,01%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>3992</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>1378</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>8225</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>6,47%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>2,24%</t>
-        </is>
-      </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>12,91%</t>
         </is>
       </c>
     </row>
@@ -1906,7 +1906,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3517</t>
+          <t>3302</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3024</t>
+          <t>3239</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,25%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10203</t>
+          <t>9703</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19156</t>
+          <t>18633</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>29,33%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>57,91%</t>
+          <t>56,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>19567</t>
+          <t>19212</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>31908</t>
+          <t>30979</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>35,75%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>59,37%</t>
+          <t>57,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>31605</t>
+          <t>32242</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>47570</t>
+          <t>47517</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>36,4%</t>
+          <t>37,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>54,79%</t>
+          <t>54,73%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13282</t>
+          <t>13619</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>22098</t>
+          <t>22695</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>40,15%</t>
+          <t>41,17%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>66,8%</t>
+          <t>68,61%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17045</t>
+          <t>16438</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>28636</t>
+          <t>28275</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>53,28%</t>
+          <t>52,61%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>33156</t>
+          <t>33055</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>48595</t>
+          <t>48724</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>38,19%</t>
+          <t>38,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>55,97%</t>
+          <t>56,12%</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3671</t>
+          <t>3646</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1333</t>
+          <t>1515</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7477</t>
+          <t>8058</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1597</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>9151</t>
+          <t>8952</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,31%</t>
         </is>
       </c>
     </row>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3407</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2755</t>
+          <t>2825</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,25%</t>
         </is>
       </c>
     </row>
@@ -2588,7 +2588,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4846</t>
+          <t>4297</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4808</t>
+          <t>4824</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,56%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>35502</t>
+          <t>35918</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>50688</t>
+          <t>50726</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>40,43%</t>
+          <t>40,9%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>57,72%</t>
+          <t>57,76%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>46803</t>
+          <t>48158</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>62998</t>
+          <t>63895</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>49,86%</t>
+          <t>51,31%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>67,12%</t>
+          <t>68,08%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>88387</t>
+          <t>88268</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>110111</t>
+          <t>109518</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>48,65%</t>
+          <t>48,59%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>60,61%</t>
+          <t>60,28%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>34042</t>
+          <t>34323</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>49118</t>
+          <t>48941</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>38,77%</t>
+          <t>39,09%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>55,93%</t>
+          <t>55,73%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>25061</t>
+          <t>24767</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>40756</t>
+          <t>40237</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>43,42%</t>
+          <t>42,87%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>62863</t>
+          <t>61912</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>83807</t>
+          <t>84124</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>34,08%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>46,13%</t>
+          <t>46,31%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1193</t>
+          <t>1128</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>6638</t>
+          <t>6796</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1995</t>
+          <t>1934</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>9312</t>
+          <t>8657</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>4519</t>
+          <t>4416</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>12984</t>
+          <t>13617</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,5%</t>
         </is>
       </c>
     </row>
@@ -3157,7 +3157,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2816</t>
+          <t>3086</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3192,7 +3192,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2890</t>
+          <t>3277</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,8%</t>
         </is>
       </c>
     </row>
@@ -3270,7 +3270,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3752</t>
+          <t>3586</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3305,7 +3305,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3348</t>
+          <t>3337</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>21692</t>
+          <t>21347</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>33152</t>
+          <t>33028</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>39,82%</t>
+          <t>39,18%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>60,85%</t>
+          <t>60,63%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>34024</t>
+          <t>34592</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>47085</t>
+          <t>47704</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>48,52%</t>
+          <t>49,33%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>67,14%</t>
+          <t>68,03%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>58654</t>
+          <t>59202</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>76362</t>
+          <t>76985</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>47,07%</t>
+          <t>47,51%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>61,28%</t>
+          <t>61,78%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>12379</t>
+          <t>12377</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>23565</t>
+          <t>23848</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>43,26%</t>
+          <t>43,78%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>22042</t>
+          <t>21278</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>34793</t>
+          <t>34453</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>30,34%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>49,61%</t>
+          <t>49,13%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>37601</t>
+          <t>37298</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>54269</t>
+          <t>54606</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>29,93%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>43,55%</t>
+          <t>43,82%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>4690</t>
+          <t>4633</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>13800</t>
+          <t>13409</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3368</t>
+          <t>3655</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>4685</t>
+          <t>4912</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>14343</t>
+          <t>14688</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,79%</t>
         </is>
       </c>
     </row>
@@ -3804,7 +3804,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>4410</t>
+          <t>4502</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3819,7 +3819,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>4442</t>
+          <t>4425</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,55%</t>
         </is>
       </c>
     </row>
@@ -3952,7 +3952,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2776</t>
+          <t>3141</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3967,7 +3967,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>2973</t>
+          <t>2855</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4002,7 +4002,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>14248</t>
+          <t>13381</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>24618</t>
+          <t>24077</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>34,1%</t>
+          <t>32,03%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>58,93%</t>
+          <t>57,63%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>13300</t>
+          <t>13245</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>22562</t>
+          <t>22708</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>36,93%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>62,91%</t>
+          <t>63,32%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>29916</t>
+          <t>30115</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>43725</t>
+          <t>43514</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>38,53%</t>
+          <t>38,79%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>56,32%</t>
+          <t>56,05%</t>
         </is>
       </c>
     </row>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>13714</t>
+          <t>13579</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>24491</t>
+          <t>24307</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4270,12 +4270,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>32,82%</t>
+          <t>32,5%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>58,62%</t>
+          <t>58,18%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4290,12 +4290,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>10130</t>
+          <t>10044</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>19169</t>
+          <t>19593</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>53,45%</t>
+          <t>54,63%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>26894</t>
+          <t>25893</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>40147</t>
+          <t>40059</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>33,35%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>51,71%</t>
+          <t>51,59%</t>
         </is>
       </c>
     </row>
@@ -4368,12 +4368,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>784</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>6820</t>
+          <t>6866</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4383,12 +4383,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4403,12 +4403,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1247</t>
+          <t>1279</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>7193</t>
+          <t>6960</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>3130</t>
+          <t>2872</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>11095</t>
+          <t>10834</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>13,95%</t>
         </is>
       </c>
     </row>
@@ -4486,7 +4486,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>4560</t>
+          <t>4110</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4501,7 +4501,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>4764</t>
+          <t>4449</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4571,7 +4571,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>5,73%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>127439</t>
+          <t>126732</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>154181</t>
+          <t>155467</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>43,24%</t>
+          <t>43,0%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>52,32%</t>
+          <t>52,75%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>164386</t>
+          <t>165385</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>193322</t>
+          <t>193769</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>50,36%</t>
+          <t>50,67%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>59,22%</t>
+          <t>59,36%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>300428</t>
+          <t>300344</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>339788</t>
+          <t>340854</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>48,37%</t>
+          <t>48,35%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>54,7%</t>
+          <t>54,88%</t>
         </is>
       </c>
     </row>
@@ -4937,12 +4937,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>118778</t>
+          <t>118492</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>145299</t>
+          <t>146732</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4952,12 +4952,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>40,3%</t>
+          <t>40,21%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>49,3%</t>
+          <t>49,79%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4972,12 +4972,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>114259</t>
+          <t>114176</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>141579</t>
+          <t>141844</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4987,12 +4987,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>35,0%</t>
+          <t>34,98%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>43,37%</t>
+          <t>43,45%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>241072</t>
+          <t>238736</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>279719</t>
+          <t>279760</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5022,12 +5022,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>38,81%</t>
+          <t>38,44%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>45,03%</t>
+          <t>45,04%</t>
         </is>
       </c>
     </row>
@@ -5050,12 +5050,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>12935</t>
+          <t>12717</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>26515</t>
+          <t>26479</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5065,12 +5065,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>8618</t>
+          <t>8700</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>19683</t>
+          <t>20326</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>24791</t>
+          <t>24233</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>43143</t>
+          <t>42472</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,84%</t>
         </is>
       </c>
     </row>
@@ -5163,12 +5163,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>1181</t>
+          <t>1170</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>6934</t>
+          <t>6892</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5183,7 +5183,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>573</t>
+          <t>566</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>5077</t>
+          <t>5342</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>2462</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>9637</t>
+          <t>10283</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,66%</t>
         </is>
       </c>
     </row>
@@ -5311,12 +5311,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>1337</t>
+          <t>1316</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>7771</t>
+          <t>7916</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5326,12 +5326,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5346,12 +5346,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>1360</t>
+          <t>1844</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>7845</t>
+          <t>8239</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5361,12 +5361,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,33%</t>
         </is>
       </c>
     </row>
@@ -5545,7 +5545,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haber podido correr bien en 2012 (tasa de respuesta: 97,91%)</t>
+          <t>Menores según la frecuencia de haber podido correr bien, percibida por el adulto en 2012 (tasa de respuesta: 97,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5740,12 +5740,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11620</t>
+          <t>11670</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21836</t>
+          <t>21832</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5755,12 +5755,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>55,22%</t>
+          <t>55,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5775,12 +5775,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12053</t>
+          <t>12396</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21669</t>
+          <t>21991</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>35,57%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>62,18%</t>
+          <t>63,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5810,12 +5810,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>27006</t>
+          <t>26358</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>40353</t>
+          <t>40363</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>35,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>54,24%</t>
+          <t>54,26%</t>
         </is>
       </c>
     </row>
@@ -5853,12 +5853,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12069</t>
+          <t>12336</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23253</t>
+          <t>22630</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5868,12 +5868,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>31,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>58,81%</t>
+          <t>57,23%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5888,12 +5888,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9799</t>
+          <t>10357</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19254</t>
+          <t>19314</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>29,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>55,25%</t>
+          <t>55,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5923,12 +5923,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>25621</t>
+          <t>24935</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>39295</t>
+          <t>39431</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>34,44%</t>
+          <t>33,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>52,82%</t>
+          <t>53,0%</t>
         </is>
       </c>
     </row>
@@ -5966,12 +5966,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2335</t>
+          <t>2723</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9623</t>
+          <t>9852</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5981,12 +5981,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6001,12 +6001,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>682</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6034</t>
+          <t>5989</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3998</t>
+          <t>4218</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>13456</t>
+          <t>13727</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>18,45%</t>
         </is>
       </c>
     </row>
@@ -6119,7 +6119,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3538</t>
+          <t>4165</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6134,7 +6134,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6154,7 +6154,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3621</t>
+          <t>3659</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6169,7 +6169,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,92%</t>
         </is>
       </c>
     </row>
@@ -6422,12 +6422,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9713</t>
+          <t>9509</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19019</t>
+          <t>18793</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6437,12 +6437,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>55,88%</t>
+          <t>55,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6457,12 +6457,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12033</t>
+          <t>12108</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21824</t>
+          <t>21666</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>34,28%</t>
+          <t>34,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>62,17%</t>
+          <t>61,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>24057</t>
+          <t>23930</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>37910</t>
+          <t>37459</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>34,79%</t>
+          <t>34,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>54,83%</t>
+          <t>54,18%</t>
         </is>
       </c>
     </row>
@@ -6535,12 +6535,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13063</t>
+          <t>13373</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>22499</t>
+          <t>22784</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6550,12 +6550,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>38,38%</t>
+          <t>39,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>66,1%</t>
+          <t>66,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11526</t>
+          <t>11875</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>21100</t>
+          <t>20979</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>32,83%</t>
+          <t>33,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>60,11%</t>
+          <t>59,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6605,7 +6605,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>27859</t>
+          <t>27897</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -6620,7 +6620,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>40,29%</t>
+          <t>40,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -6653,7 +6653,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4165</t>
+          <t>4748</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6668,7 +6668,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>602</t>
+          <t>600</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5029</t>
+          <t>5116</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6703,7 +6703,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1209</t>
+          <t>1246</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>6636</t>
+          <t>7221</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>10,44%</t>
         </is>
       </c>
     </row>
@@ -6766,92 +6766,92 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
+          <t>3541</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,99%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>10,4%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>678</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
           <t>3429</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>1,99%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,98%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>10,08%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>678</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>3457</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,98%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,96%</t>
         </is>
       </c>
     </row>
@@ -7104,12 +7104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10696</t>
+          <t>10321</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20753</t>
+          <t>20657</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>46,83%</t>
+          <t>46,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9648</t>
+          <t>10127</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18703</t>
+          <t>19110</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7154,12 +7154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>31,63%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>58,42%</t>
+          <t>59,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>23247</t>
+          <t>22866</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>36837</t>
+          <t>36332</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7189,12 +7189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>48,26%</t>
+          <t>47,6%</t>
         </is>
       </c>
     </row>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>19046</t>
+          <t>19505</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>29981</t>
+          <t>30170</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>42,98%</t>
+          <t>44,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>67,65%</t>
+          <t>68,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11613</t>
+          <t>11535</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>20753</t>
+          <t>20649</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7267,12 +7267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>36,03%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>64,83%</t>
+          <t>64,5%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>33845</t>
+          <t>33943</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>47342</t>
+          <t>47738</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7302,12 +7302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>44,34%</t>
+          <t>44,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>62,02%</t>
+          <t>62,54%</t>
         </is>
       </c>
     </row>
@@ -7330,12 +7330,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1523</t>
+          <t>1525</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7923</t>
+          <t>8557</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7350,7 +7350,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>438</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4785</t>
+          <t>4459</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2924</t>
+          <t>2857</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>10793</t>
+          <t>10180</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7415,12 +7415,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>13,34%</t>
         </is>
       </c>
     </row>
@@ -7786,12 +7786,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>26738</t>
+          <t>27038</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>41811</t>
+          <t>41694</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>31,13%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>48,14%</t>
+          <t>48,0%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>36308</t>
+          <t>36402</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>52284</t>
+          <t>53355</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7836,12 +7836,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>36,89%</t>
+          <t>36,98%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>53,12%</t>
+          <t>54,2%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>66890</t>
+          <t>68278</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>89583</t>
+          <t>89819</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7871,12 +7871,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>36,1%</t>
+          <t>36,85%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>48,35%</t>
+          <t>48,47%</t>
         </is>
       </c>
     </row>
@@ -7899,12 +7899,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>37807</t>
+          <t>37746</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>52660</t>
+          <t>53298</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7914,12 +7914,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>43,53%</t>
+          <t>43,46%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>60,63%</t>
+          <t>61,36%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7934,12 +7934,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>40014</t>
+          <t>39236</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>56222</t>
+          <t>55782</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7949,12 +7949,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>40,65%</t>
+          <t>39,86%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>57,12%</t>
+          <t>56,67%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7969,12 +7969,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>81846</t>
+          <t>81219</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>105217</t>
+          <t>102606</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7984,12 +7984,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>44,17%</t>
+          <t>43,83%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>56,79%</t>
+          <t>55,38%</t>
         </is>
       </c>
     </row>
@@ -8012,12 +8012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2677</t>
+          <t>2791</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>11131</t>
+          <t>10754</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8027,47 +8027,47 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
+          <t>3,21%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>12,38%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>3036</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>1164</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>6753</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
           <t>3,08%</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>12,82%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>3036</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>1186</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>6678</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>3,08%</t>
-        </is>
-      </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8082,12 +8082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>5182</t>
+          <t>4484</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>14933</t>
+          <t>14679</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,92%</t>
         </is>
       </c>
     </row>
@@ -8130,7 +8130,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4176</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8145,7 +8145,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8160,12 +8160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>621</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5165</t>
+          <t>5010</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8175,12 +8175,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8195,12 +8195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1073</t>
+          <t>1087</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>6623</t>
+          <t>6967</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8210,12 +8210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,76%</t>
         </is>
       </c>
     </row>
@@ -8243,7 +8243,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3391</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8258,7 +8258,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8278,7 +8278,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4496</t>
+          <t>3903</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8308,12 +8308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>628</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5167</t>
+          <t>5650</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8328,7 +8328,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>3,05%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>22394</t>
+          <t>21884</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>35894</t>
+          <t>36187</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>47,18%</t>
+          <t>47,57%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>23579</t>
+          <t>23539</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>37433</t>
+          <t>37346</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>32,66%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>51,94%</t>
+          <t>51,82%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>48702</t>
+          <t>49596</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>67913</t>
+          <t>69651</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>33,48%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>45,84%</t>
+          <t>47,02%</t>
         </is>
       </c>
     </row>
@@ -8581,12 +8581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>35735</t>
+          <t>35939</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>49995</t>
+          <t>50935</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8596,12 +8596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>46,97%</t>
+          <t>47,24%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>65,72%</t>
+          <t>66,95%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8616,12 +8616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>25546</t>
+          <t>25802</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>39715</t>
+          <t>39281</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8631,12 +8631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>35,8%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>55,11%</t>
+          <t>54,51%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8651,12 +8651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>66481</t>
+          <t>65851</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>85688</t>
+          <t>85447</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8666,12 +8666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>44,88%</t>
+          <t>44,45%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>57,84%</t>
+          <t>57,68%</t>
         </is>
       </c>
     </row>
@@ -8694,12 +8694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1453</t>
+          <t>1460</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>9116</t>
+          <t>8373</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8709,12 +8709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8729,12 +8729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2616</t>
+          <t>2927</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>11766</t>
+          <t>11320</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8744,12 +8744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>5760</t>
+          <t>5962</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>16621</t>
+          <t>17925</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8779,12 +8779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>12,1%</t>
         </is>
       </c>
     </row>
@@ -8842,12 +8842,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>648</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>6271</t>
+          <t>6029</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8862,7 +8862,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>649</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>6559</t>
+          <t>6595</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8897,7 +8897,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,45%</t>
         </is>
       </c>
     </row>
@@ -8960,7 +8960,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3491</t>
+          <t>3629</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8975,7 +8975,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8995,7 +8995,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>3462</t>
+          <t>4186</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9010,7 +9010,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,83%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>4050</t>
+          <t>4128</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>11329</t>
+          <t>11686</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>45,53%</t>
+          <t>46,97%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>14055</t>
+          <t>14560</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>23953</t>
+          <t>24692</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>37,57%</t>
+          <t>38,92%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>64,03%</t>
+          <t>66,0%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>20742</t>
+          <t>20486</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>33789</t>
+          <t>33392</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>32,89%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>54,24%</t>
+          <t>53,6%</t>
         </is>
       </c>
     </row>
@@ -9263,12 +9263,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>11314</t>
+          <t>10869</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>19013</t>
+          <t>18785</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9278,12 +9278,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>45,47%</t>
+          <t>43,68%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>76,41%</t>
+          <t>75,5%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9298,12 +9298,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>9442</t>
+          <t>9063</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>19018</t>
+          <t>18702</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9313,12 +9313,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>50,83%</t>
+          <t>49,99%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9333,12 +9333,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>21954</t>
+          <t>22654</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>35327</t>
+          <t>35895</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9348,12 +9348,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>35,24%</t>
+          <t>36,37%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>56,71%</t>
+          <t>57,62%</t>
         </is>
       </c>
     </row>
@@ -9381,7 +9381,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>4341</t>
+          <t>4940</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>1238</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>7354</t>
+          <t>6971</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>2047</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>9108</t>
+          <t>9200</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,77%</t>
         </is>
       </c>
     </row>
@@ -9494,7 +9494,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>4109</t>
+          <t>4064</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9509,7 +9509,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9564,7 +9564,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>4128</t>
+          <t>4925</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9579,7 +9579,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>7,91%</t>
         </is>
       </c>
     </row>
@@ -9642,7 +9642,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>4298</t>
+          <t>4325</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -9657,7 +9657,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9677,7 +9677,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>4389</t>
+          <t>4049</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9692,7 +9692,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,5%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>102363</t>
+          <t>102147</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>130107</t>
+          <t>131330</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>33,41%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>42,56%</t>
+          <t>42,96%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>128470</t>
+          <t>128725</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>156825</t>
+          <t>156507</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>41,46%</t>
+          <t>41,54%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>50,61%</t>
+          <t>50,51%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>239152</t>
+          <t>238710</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>279132</t>
+          <t>277322</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>38,85%</t>
+          <t>38,78%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>45,34%</t>
+          <t>45,05%</t>
         </is>
       </c>
     </row>
@@ -9945,12 +9945,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>151202</t>
+          <t>150547</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>180127</t>
+          <t>179133</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -9960,12 +9960,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>49,46%</t>
+          <t>49,24%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>58,92%</t>
+          <t>58,59%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -9980,12 +9980,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>126054</t>
+          <t>126903</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>155153</t>
+          <t>154918</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>40,68%</t>
+          <t>40,95%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>50,07%</t>
+          <t>49,99%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10015,12 +10015,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>283884</t>
+          <t>284387</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>324886</t>
+          <t>324436</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>46,12%</t>
+          <t>46,2%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>52,78%</t>
+          <t>52,7%</t>
         </is>
       </c>
     </row>
@@ -10058,12 +10058,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>15134</t>
+          <t>15749</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>31811</t>
+          <t>30568</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10073,12 +10073,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10093,12 +10093,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>12482</t>
+          <t>12474</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>26574</t>
+          <t>26714</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10113,7 +10113,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>31942</t>
+          <t>31761</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>53515</t>
+          <t>51513</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,37%</t>
         </is>
       </c>
     </row>
@@ -10171,12 +10171,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>699</t>
+          <t>697</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>6479</t>
+          <t>6555</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -10191,7 +10191,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -10206,12 +10206,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>2105</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>9936</t>
+          <t>9412</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>3349</t>
+          <t>4041</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>12443</t>
+          <t>13401</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,18%</t>
         </is>
       </c>
     </row>
@@ -10289,7 +10289,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>3286</t>
+          <t>3969</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -10304,7 +10304,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -10319,12 +10319,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>1258</t>
+          <t>1259</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>7166</t>
+          <t>7048</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -10339,7 +10339,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>1338</t>
+          <t>1318</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>7851</t>
+          <t>8328</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,35%</t>
         </is>
       </c>
     </row>
@@ -10553,7 +10553,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haber podido correr bien en 2016 (tasa de respuesta: 98,72%)</t>
+          <t>Menores según la frecuencia de haber podido correr bien, percibida por el adulto en 2016 (tasa de respuesta: 98,72%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13158</t>
+          <t>12888</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22510</t>
+          <t>22748</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10763,12 +10763,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>38,01%</t>
+          <t>37,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>65,03%</t>
+          <t>65,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10783,12 +10783,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21061</t>
+          <t>20907</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>30672</t>
+          <t>30471</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10798,12 +10798,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>55,0%</t>
+          <t>54,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>80,1%</t>
+          <t>79,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10818,12 +10818,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>37114</t>
+          <t>37245</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>50688</t>
+          <t>50853</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10833,12 +10833,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>50,91%</t>
+          <t>51,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>69,52%</t>
+          <t>69,75%</t>
         </is>
       </c>
     </row>
@@ -10861,12 +10861,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10692</t>
+          <t>10493</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20165</t>
+          <t>20412</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10876,12 +10876,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,89%</t>
+          <t>30,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>58,25%</t>
+          <t>58,96%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10896,12 +10896,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5006</t>
+          <t>4852</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14307</t>
+          <t>14259</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10911,12 +10911,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>37,36%</t>
+          <t>37,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10931,12 +10931,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>17940</t>
+          <t>17324</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>31180</t>
+          <t>30752</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10946,12 +10946,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>42,77%</t>
+          <t>42,18%</t>
         </is>
       </c>
     </row>
@@ -10979,7 +10979,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5322</t>
+          <t>5348</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10994,7 +10994,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11009,12 +11009,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>634</t>
+          <t>637</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5797</t>
+          <t>5940</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11029,7 +11029,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11044,12 +11044,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1393</t>
+          <t>1427</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>8006</t>
+          <t>8390</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11059,12 +11059,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,51%</t>
         </is>
       </c>
     </row>
@@ -11127,7 +11127,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3645</t>
+          <t>3768</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11142,7 +11142,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11162,7 +11162,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3570</t>
+          <t>3633</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11177,7 +11177,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,98%</t>
         </is>
       </c>
     </row>
@@ -11430,12 +11430,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17044</t>
+          <t>17538</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>29218</t>
+          <t>29095</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11445,12 +11445,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>33,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>55,68%</t>
+          <t>55,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11465,12 +11465,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>28380</t>
+          <t>28560</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>38764</t>
+          <t>38767</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11480,12 +11480,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>58,58%</t>
+          <t>58,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>80,02%</t>
+          <t>80,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11500,12 +11500,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>48504</t>
+          <t>48242</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>65504</t>
+          <t>64730</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11515,12 +11515,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>48,06%</t>
+          <t>47,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>64,91%</t>
+          <t>64,14%</t>
         </is>
       </c>
     </row>
@@ -11543,12 +11543,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19464</t>
+          <t>19590</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>31805</t>
+          <t>31410</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11558,12 +11558,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>37,33%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>60,61%</t>
+          <t>59,86%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11578,12 +11578,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8359</t>
+          <t>7912</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18200</t>
+          <t>17922</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11593,12 +11593,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>37,57%</t>
+          <t>37,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11613,12 +11613,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>30286</t>
+          <t>30389</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>46188</t>
+          <t>47251</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11628,12 +11628,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>45,77%</t>
+          <t>46,82%</t>
         </is>
       </c>
     </row>
@@ -11656,12 +11656,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>956</t>
+          <t>1003</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8215</t>
+          <t>7929</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11671,12 +11671,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11696,7 +11696,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3794</t>
+          <t>3747</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11711,7 +11711,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1436</t>
+          <t>1437</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>9243</t>
+          <t>9846</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11746,7 +11746,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,76%</t>
         </is>
       </c>
     </row>
@@ -11774,7 +11774,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3169</t>
+          <t>3126</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11789,7 +11789,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3937</t>
+          <t>4317</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11824,7 +11824,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11844,7 +11844,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4663</t>
+          <t>4612</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11859,7 +11859,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,57%</t>
         </is>
       </c>
     </row>
@@ -12112,12 +12112,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12393</t>
+          <t>11823</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20545</t>
+          <t>20713</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12127,12 +12127,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>44,1%</t>
+          <t>42,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>73,11%</t>
+          <t>73,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12147,12 +12147,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14364</t>
+          <t>14379</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>25189</t>
+          <t>25508</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12162,12 +12162,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>35,07%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>61,43%</t>
+          <t>62,21%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12182,12 +12182,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>28944</t>
+          <t>29823</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>43272</t>
+          <t>43178</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12197,12 +12197,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>41,88%</t>
+          <t>43,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>62,62%</t>
+          <t>62,48%</t>
         </is>
       </c>
     </row>
@@ -12225,12 +12225,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5400</t>
+          <t>4976</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13661</t>
+          <t>13431</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12240,12 +12240,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>48,61%</t>
+          <t>47,79%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12260,12 +12260,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13501</t>
+          <t>12962</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>24265</t>
+          <t>23934</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12275,12 +12275,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>31,61%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>59,18%</t>
+          <t>58,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>21486</t>
+          <t>21150</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>35569</t>
+          <t>34237</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12310,12 +12310,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>51,47%</t>
+          <t>49,54%</t>
         </is>
       </c>
     </row>
@@ -12343,7 +12343,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3912</t>
+          <t>3941</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12358,7 +12358,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12373,12 +12373,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>699</t>
+          <t>721</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6362</t>
+          <t>6329</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12388,12 +12388,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12408,12 +12408,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1890</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>8700</t>
+          <t>8115</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>11,74%</t>
         </is>
       </c>
     </row>
@@ -12456,7 +12456,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3128</t>
+          <t>3104</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12471,7 +12471,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12526,7 +12526,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3775</t>
+          <t>2538</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12541,7 +12541,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>3,67%</t>
         </is>
       </c>
     </row>
@@ -12569,7 +12569,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2681</t>
+          <t>3121</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12584,7 +12584,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12639,7 +12639,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3735</t>
+          <t>3305</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12654,7 +12654,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>4,78%</t>
         </is>
       </c>
     </row>
@@ -12794,12 +12794,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>56294</t>
+          <t>56221</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>73575</t>
+          <t>73449</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12809,12 +12809,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>48,9%</t>
+          <t>48,84%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>63,91%</t>
+          <t>63,8%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12829,12 +12829,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>62649</t>
+          <t>62090</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>78338</t>
+          <t>77923</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12844,12 +12844,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>60,9%</t>
+          <t>60,36%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>76,16%</t>
+          <t>75,75%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12864,12 +12864,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>123511</t>
+          <t>123560</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>146998</t>
+          <t>146457</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12879,12 +12879,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>56,66%</t>
+          <t>56,68%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>67,43%</t>
+          <t>67,19%</t>
         </is>
       </c>
     </row>
@@ -12907,12 +12907,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>34198</t>
+          <t>34498</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>50091</t>
+          <t>51647</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12922,12 +12922,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>29,97%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>43,51%</t>
+          <t>44,86%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12942,12 +12942,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>21693</t>
+          <t>22113</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>37410</t>
+          <t>37116</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12957,12 +12957,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>60637</t>
+          <t>60551</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>83271</t>
+          <t>83531</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12992,12 +12992,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>38,2%</t>
+          <t>38,32%</t>
         </is>
       </c>
     </row>
@@ -13020,12 +13020,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2668</t>
+          <t>2578</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>9768</t>
+          <t>10859</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13035,12 +13035,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13055,12 +13055,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>585</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6373</t>
+          <t>6376</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13090,12 +13090,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>4124</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>13705</t>
+          <t>13809</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13105,12 +13105,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,33%</t>
         </is>
       </c>
     </row>
@@ -13133,12 +13133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>614</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7384</t>
+          <t>6499</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13148,12 +13148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13173,7 +13173,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4227</t>
+          <t>4069</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13188,7 +13188,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13203,12 +13203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>709</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>7172</t>
+          <t>7223</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13218,12 +13218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,31%</t>
         </is>
       </c>
     </row>
@@ -13476,12 +13476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>37630</t>
+          <t>38139</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>51604</t>
+          <t>51693</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13491,12 +13491,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>49,49%</t>
+          <t>50,15%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>67,86%</t>
+          <t>67,98%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13511,12 +13511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>38746</t>
+          <t>38176</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>52233</t>
+          <t>52222</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13526,12 +13526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>53,13%</t>
+          <t>52,35%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>71,62%</t>
+          <t>71,61%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13546,12 +13546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>80491</t>
+          <t>79525</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>100190</t>
+          <t>100736</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13561,12 +13561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>54,03%</t>
+          <t>53,38%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>67,25%</t>
+          <t>67,62%</t>
         </is>
       </c>
     </row>
@@ -13589,12 +13589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>20575</t>
+          <t>20993</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>34444</t>
+          <t>34238</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>45,29%</t>
+          <t>45,02%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13624,12 +13624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>16463</t>
+          <t>16813</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>29648</t>
+          <t>30683</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13639,12 +13639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>40,65%</t>
+          <t>42,07%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13659,12 +13659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>41120</t>
+          <t>40811</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>60416</t>
+          <t>60444</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13674,12 +13674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>40,55%</t>
+          <t>40,57%</t>
         </is>
       </c>
     </row>
@@ -13702,12 +13702,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>879</t>
+          <t>892</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>7172</t>
+          <t>7000</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13717,12 +13717,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -13742,7 +13742,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>4249</t>
+          <t>4060</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13757,7 +13757,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -13772,12 +13772,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1514</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>9271</t>
+          <t>8803</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -13787,12 +13787,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>5,91%</t>
         </is>
       </c>
     </row>
@@ -13820,7 +13820,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3761</t>
+          <t>3980</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -13835,7 +13835,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -13855,7 +13855,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>5750</t>
+          <t>6052</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -13870,7 +13870,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -13885,12 +13885,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>769</t>
+          <t>759</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>6601</t>
+          <t>6709</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -13900,12 +13900,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,5%</t>
         </is>
       </c>
     </row>
@@ -13968,7 +13968,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>4762</t>
+          <t>5429</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -13983,7 +13983,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -14003,7 +14003,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5607</t>
+          <t>4930</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14018,7 +14018,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,31%</t>
         </is>
       </c>
     </row>
@@ -14158,12 +14158,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>12182</t>
+          <t>12045</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>21481</t>
+          <t>21509</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -14173,12 +14173,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>38,67%</t>
+          <t>38,23%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>68,18%</t>
+          <t>68,27%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -14193,12 +14193,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>23491</t>
+          <t>23685</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>32381</t>
+          <t>32521</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -14208,12 +14208,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>60,76%</t>
+          <t>61,26%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>84,12%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -14228,12 +14228,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>38851</t>
+          <t>38554</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>51445</t>
+          <t>51402</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -14243,12 +14243,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>55,37%</t>
+          <t>54,95%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>73,32%</t>
+          <t>73,26%</t>
         </is>
       </c>
     </row>
@@ -14271,12 +14271,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>6803</t>
+          <t>6879</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>16265</t>
+          <t>15592</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -14286,12 +14286,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>51,63%</t>
+          <t>49,49%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -14306,12 +14306,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>4448</t>
+          <t>4253</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>12718</t>
+          <t>12454</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -14321,12 +14321,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>32,21%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -14341,12 +14341,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>13301</t>
+          <t>13224</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>25602</t>
+          <t>25590</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>36,49%</t>
+          <t>36,47%</t>
         </is>
       </c>
     </row>
@@ -14384,12 +14384,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>766</t>
+          <t>776</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>6677</t>
+          <t>7460</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -14399,12 +14399,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -14424,7 +14424,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>4788</t>
+          <t>4391</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -14439,7 +14439,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -14454,12 +14454,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1465</t>
+          <t>1425</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>8759</t>
+          <t>9022</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -14469,12 +14469,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,86%</t>
         </is>
       </c>
     </row>
@@ -14615,7 +14615,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>3998</t>
+          <t>3912</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -14630,7 +14630,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -14650,7 +14650,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>3825</t>
+          <t>3737</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -14665,7 +14665,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -14685,7 +14685,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>5369</t>
+          <t>5167</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -14700,7 +14700,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,36%</t>
         </is>
       </c>
     </row>
@@ -14840,12 +14840,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>169692</t>
+          <t>168368</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>199859</t>
+          <t>200036</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -14855,12 +14855,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>50,22%</t>
+          <t>49,83%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>59,15%</t>
+          <t>59,21%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -14875,12 +14875,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>209764</t>
+          <t>207917</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>239485</t>
+          <t>239401</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -14890,12 +14890,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>61,3%</t>
+          <t>60,76%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>69,99%</t>
+          <t>69,96%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -14910,12 +14910,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>387115</t>
+          <t>388167</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>431418</t>
+          <t>430254</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -14925,12 +14925,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>56,92%</t>
+          <t>57,08%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>63,44%</t>
+          <t>63,27%</t>
         </is>
       </c>
     </row>
@@ -14953,12 +14953,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>115147</t>
+          <t>113936</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>144726</t>
+          <t>146212</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -14968,12 +14968,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>33,72%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>42,83%</t>
+          <t>43,27%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -14988,12 +14988,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>86320</t>
+          <t>86656</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>114989</t>
+          <t>115693</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>33,6%</t>
+          <t>33,81%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -15023,12 +15023,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>209810</t>
+          <t>210500</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>252193</t>
+          <t>249913</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -15038,12 +15038,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>37,08%</t>
+          <t>36,75%</t>
         </is>
       </c>
     </row>
@@ -15066,12 +15066,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>10887</t>
+          <t>11699</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>25930</t>
+          <t>26201</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -15081,47 +15081,47 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
+          <t>3,46%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>7,75%</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>11020</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>6004</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>18099</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
           <t>3,22%</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>7,67%</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>11020</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr">
-        <is>
-          <t>6705</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>17274</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr">
-        <is>
-          <t>3,22%</t>
-        </is>
-      </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>19796</t>
+          <t>21166</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>37288</t>
+          <t>39295</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,78%</t>
         </is>
       </c>
     </row>
@@ -15179,12 +15179,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>1650</t>
+          <t>1644</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>9336</t>
+          <t>9292</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -15199,7 +15199,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -15214,12 +15214,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>1470</t>
+          <t>1461</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>8862</t>
+          <t>8613</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -15234,7 +15234,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -15249,12 +15249,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>4235</t>
+          <t>4315</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>14109</t>
+          <t>14161</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -15264,12 +15264,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -15297,7 +15297,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>5262</t>
+          <t>4445</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -15312,7 +15312,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -15327,12 +15327,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>718</t>
+          <t>721</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>6225</t>
+          <t>7000</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -15347,7 +15347,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -15362,12 +15362,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>1405</t>
+          <t>1337</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>8075</t>
+          <t>7798</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -15377,12 +15377,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
